--- a/apps/web/src/lib/utils/__fixtures__/export-results.xlsx
+++ b/apps/web/src/lib/utils/__fixtures__/export-results.xlsx
@@ -365,13 +365,13 @@
     <t>Calculation methods version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Calculation methods changed</t>
   </si>
   <si>
-    <t>This project was last solved with calculation methods version 1.1.0. These results use version 1.3.0, so some values may differ from the ones it was shared with.</t>
+    <t>This project was last solved with calculation methods version 1.1.0. These results use version 1.4.0, so some values may differ from the ones it was shared with.</t>
   </si>
   <si>
     <t>Server library: CoolProp</t>
@@ -1412,7 +1412,7 @@
     <t>Case: base case</t>
   </si>
   <si>
-    <t>OpenSolve Pipe calculation methods version 1.3.0</t>
+    <t>OpenSolve Pipe calculation methods version 1.4.0</t>
   </si>
   <si>
     <t>Solved: 2026-10-25T12:30:00Z</t>

--- a/apps/web/src/lib/utils/__fixtures__/export-results.xlsx
+++ b/apps/web/src/lib/utils/__fixtures__/export-results.xlsx
@@ -377,13 +377,13 @@
     <t>Calculation methods version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Calculation methods changed</t>
   </si>
   <si>
-    <t>This project was last solved with calculation methods version 1.1.0. These results use version 1.4.0, so some values may differ from the ones it was shared with.</t>
+    <t>This project was last solved with calculation methods version 1.1.0. These results use version 1.5.0, so some values may differ from the ones it was shared with.</t>
   </si>
   <si>
     <t>Server library: CoolProp</t>
@@ -1556,7 +1556,7 @@
     <t>Case: base case</t>
   </si>
   <si>
-    <t>OpenSolve Pipe calculation methods version 1.4.0</t>
+    <t>OpenSolve Pipe calculation methods version 1.5.0</t>
   </si>
   <si>
     <t>Solved: 2026-10-25T12:30:00Z</t>
